--- a/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
+++ b/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="280">
   <si>
     <t>#</t>
   </si>
@@ -171,9 +171,6 @@
     <t>J4, J5</t>
   </si>
   <si>
-    <t>J6</t>
-  </si>
-  <si>
     <t>J7</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>Gold 250V 3A Straight Square Pins 2.5mm 2P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
-    <t>CABLE ADAPTER 6 POS</t>
-  </si>
-  <si>
     <t>Gold 250V 3A Straight Square Pins 2.5mm 3P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x3P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
@@ -600,9 +594,6 @@
     <t>X6511WV-02H-C60D30</t>
   </si>
   <si>
-    <t>TC2030-IDC</t>
-  </si>
-  <si>
     <t>X6511WV-03H-C60D30</t>
   </si>
   <si>
@@ -732,9 +723,6 @@
     <t>XKB</t>
   </si>
   <si>
-    <t>Tag-Connect</t>
-  </si>
-  <si>
     <t>YJYCOIN</t>
   </si>
   <si>
@@ -823,12 +811,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Tag Connect</t>
-  </si>
-  <si>
-    <t>DO NOT MOUNT</t>
   </si>
   <si>
     <t>Custom</t>
@@ -883,7 +865,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,13 +904,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1057,7 +1032,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1094,20 +1069,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1420,9 +1386,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1436,25 +1402,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1470,19 +1436,19 @@
         <v>24</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
@@ -1492,7 +1458,7 @@
     <row r="4" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B56" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B55" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1502,19 +1468,19 @@
         <v>25</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -1534,19 +1500,19 @@
         <v>26</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -1566,19 +1532,19 @@
         <v>27</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -1598,19 +1564,19 @@
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -1630,19 +1596,19 @@
         <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J8" s="9">
         <v>11</v>
@@ -1662,19 +1628,19 @@
         <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -1694,19 +1660,19 @@
         <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
@@ -1726,19 +1692,19 @@
         <v>32</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J11" s="7">
         <v>11</v>
@@ -1758,19 +1724,19 @@
         <v>33</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -1790,19 +1756,19 @@
         <v>34</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J13" s="7">
         <v>4</v>
@@ -1822,19 +1788,19 @@
         <v>35</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>7</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -1854,19 +1820,19 @@
         <v>36</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
@@ -1886,19 +1852,19 @@
         <v>37</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>7</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1918,19 +1884,19 @@
         <v>38</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -1950,19 +1916,19 @@
         <v>39</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -1982,19 +1948,19 @@
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -2014,19 +1980,19 @@
         <v>41</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -2046,19 +2012,19 @@
         <v>42</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2078,19 +2044,19 @@
         <v>43</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -2110,19 +2076,19 @@
         <v>44</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J23" s="7">
         <v>4</v>
@@ -2142,19 +2108,19 @@
         <v>45</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -2174,19 +2140,19 @@
         <v>46</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -2206,19 +2172,19 @@
         <v>47</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J26" s="9">
         <v>1</v>
@@ -2238,19 +2204,19 @@
         <v>48</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -2270,1079 +2236,1045 @@
         <v>49</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
-        <f>ROW(B29) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="C29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="J29" s="15">
-        <v>1</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>269</v>
-      </c>
+      <c r="E29" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J29" s="9">
+        <v>1</v>
+      </c>
+      <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B30) - ROW($B$2)</f>
         <v>28</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>236</v>
+      <c r="E30" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="J30" s="9">
-        <v>1</v>
-      </c>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="J30" s="7">
+        <v>4</v>
+      </c>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
-        <f>ROW(B31) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>108</v>
+      <c r="E31" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>234</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" s="7">
-        <v>4</v>
-      </c>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="J31" s="9">
+        <v>1</v>
+      </c>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B32) - ROW($B$2)</f>
         <v>30</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="C32" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>109</v>
+      <c r="E32" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="J32" s="9">
-        <v>1</v>
-      </c>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J32" s="7">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
-        <f>ROW(B33) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>221</v>
+      <c r="E33" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J33" s="7">
-        <v>1</v>
-      </c>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="J33" s="9">
+        <v>7</v>
+      </c>
+      <c r="K33" s="9"/>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B34) - ROW($B$2)</f>
         <v>32</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="C34" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>239</v>
+      <c r="E34" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J34" s="9">
-        <v>7</v>
-      </c>
-      <c r="K34" s="9"/>
+        <v>263</v>
+      </c>
+      <c r="J34" s="7">
+        <v>5</v>
+      </c>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
-        <f>ROW(B35) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="C35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>240</v>
+      <c r="E35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J35" s="7">
-        <v>5</v>
-      </c>
-      <c r="K35" s="7"/>
+        <v>263</v>
+      </c>
+      <c r="J35" s="9">
+        <v>1</v>
+      </c>
+      <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>7</v>
+      <c r="E36" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>225</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J36" s="9">
-        <v>1</v>
-      </c>
-      <c r="K36" s="9"/>
+        <v>263</v>
+      </c>
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
-        <f>ROW(B37) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="C37" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J37" s="7">
-        <v>1</v>
-      </c>
-      <c r="K37" s="7"/>
+      <c r="E37" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="J37" s="9">
+        <v>1</v>
+      </c>
+      <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B38) - ROW($B$2)</f>
         <v>36</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="J38" s="9">
-        <v>1</v>
-      </c>
-      <c r="K38" s="9"/>
+      <c r="E38" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" s="7">
+        <v>1</v>
+      </c>
+      <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
-        <f>ROW(B39) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="J39" s="7">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7"/>
+      <c r="E39" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="J39" s="9">
+        <v>1</v>
+      </c>
+      <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B40) - ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="C40" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E40" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="J40" s="9">
-        <v>1</v>
-      </c>
-      <c r="K40" s="9"/>
+      <c r="E40" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="J40" s="7">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
-        <f>ROW(B41) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="7" t="s">
+      <c r="C41" s="13"/>
+      <c r="D41" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="J41" s="7">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7"/>
+      <c r="E41" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="9">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B42) - ROW($B$2)</f>
         <v>40</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="9" t="s">
+      <c r="C42" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="J42" s="9">
-        <v>1</v>
-      </c>
-      <c r="K42" s="9"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="J42" s="7">
+        <v>5</v>
+      </c>
+      <c r="K42" s="7"/>
+    </row>
+    <row r="43" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
-        <f>ROW(B43) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="7" t="s">
+      <c r="C43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="J43" s="7">
-        <v>5</v>
-      </c>
-      <c r="K43" s="7"/>
-    </row>
-    <row r="44" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E43" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J43" s="9">
+        <v>12</v>
+      </c>
+      <c r="K43" s="9"/>
+    </row>
+    <row r="44" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B44) - ROW($B$2)</f>
         <v>42</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="9" t="s">
+      <c r="C44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="J44" s="9">
-        <v>12</v>
-      </c>
-      <c r="K44" s="9"/>
-    </row>
-    <row r="45" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E44" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J44" s="7">
+        <v>33</v>
+      </c>
+      <c r="K44" s="7"/>
+    </row>
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
-        <f>ROW(B45) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="7" t="s">
+      <c r="C45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="J45" s="7">
-        <v>33</v>
-      </c>
-      <c r="K45" s="7"/>
+      <c r="E45" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="J45" s="9">
+        <v>5</v>
+      </c>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B46) - ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="9">
-        <v>5</v>
-      </c>
-      <c r="K46" s="9"/>
+      <c r="E46" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J46" s="7">
+        <v>2</v>
+      </c>
+      <c r="K46" s="7"/>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f>ROW(B47) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="J47" s="7">
-        <v>2</v>
-      </c>
-      <c r="K47" s="7"/>
+      <c r="E47" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J47" s="9">
+        <v>8</v>
+      </c>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B48) - ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="C48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F48" s="9" t="s">
+      <c r="E48" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J48" s="9">
-        <v>8</v>
-      </c>
-      <c r="K48" s="9"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J48" s="7">
+        <v>2</v>
+      </c>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f>ROW(B49) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="8" t="s">
-        <v>126</v>
+      <c r="E49" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J49" s="7">
-        <v>2</v>
-      </c>
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="J49" s="9">
+        <v>1</v>
+      </c>
+      <c r="K49" s="9"/>
+    </row>
+    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B50) - ROW($B$2)</f>
         <v>48</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="9" t="s">
+      <c r="C50" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>127</v>
+      <c r="E50" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>242</v>
+        <v>164</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J50" s="9">
-        <v>1</v>
-      </c>
-      <c r="K50" s="9"/>
-    </row>
-    <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="J50" s="7">
+        <v>1</v>
+      </c>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f>ROW(B51) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>243</v>
+      <c r="E51" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J51" s="7">
-        <v>1</v>
-      </c>
-      <c r="K51" s="7"/>
+        <v>263</v>
+      </c>
+      <c r="J51" s="9">
+        <v>1</v>
+      </c>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B52) - ROW($B$2)</f>
         <v>50</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>7</v>
+      <c r="E52" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>227</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="9">
-        <v>1</v>
-      </c>
-      <c r="K52" s="9"/>
+        <v>263</v>
+      </c>
+      <c r="J52" s="7">
+        <v>1</v>
+      </c>
+      <c r="K52" s="7"/>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f>ROW(B53) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>230</v>
+      <c r="E53" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>239</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J53" s="7">
-        <v>1</v>
-      </c>
-      <c r="K53" s="7"/>
+        <v>263</v>
+      </c>
+      <c r="J53" s="9">
+        <v>1</v>
+      </c>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B54) - ROW($B$2)</f>
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>243</v>
+      <c r="E54" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J54" s="9">
-        <v>1</v>
-      </c>
-      <c r="K54" s="9"/>
+        <v>263</v>
+      </c>
+      <c r="J54" s="7">
+        <v>1</v>
+      </c>
+      <c r="K54" s="7"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f>ROW(B55) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>243</v>
+      <c r="E55" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J55" s="7">
-        <v>1</v>
-      </c>
-      <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="J55" s="9">
+        <v>1</v>
+      </c>
+      <c r="K55" s="9"/>
+    </row>
+    <row r="56" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B56) - ROW($B$2)</f>
         <v>54</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>230</v>
+      <c r="E56" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I56" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J56" s="7">
+        <v>4</v>
+      </c>
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="11">
+        <f t="shared" ref="B57" si="1">ROW(B57) - ROW($B$2)</f>
+        <v>55</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="J56" s="9">
-        <v>1</v>
-      </c>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="11">
-        <f>ROW(B57) - ROW($B$2)</f>
-        <v>55</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J57" s="7">
-        <v>4</v>
-      </c>
-      <c r="K57" s="7"/>
+      <c r="E57" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J57" s="9">
+        <v>1</v>
+      </c>
+      <c r="K57" s="9"/>
     </row>
     <row r="58" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
-        <f t="shared" ref="B58" si="1">ROW(B58) - ROW($B$2)</f>
+        <f>ROW(B58) - ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J58" s="7">
+        <v>2</v>
+      </c>
+      <c r="K58" s="7"/>
+    </row>
+    <row r="59" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="11">
+        <f t="shared" ref="B59" si="2">ROW(B59) - ROW($B$2)</f>
+        <v>57</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="K59" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D58" s="9" t="s">
+    </row>
+    <row r="60" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="11">
+        <f>ROW(B60) - ROW($B$2)</f>
+        <v>58</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E58" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="J58" s="9">
-        <v>1</v>
-      </c>
-      <c r="K58" s="9"/>
-    </row>
-    <row r="59" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="11">
-        <f>ROW(B59) - ROW($B$2)</f>
-        <v>57</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="E60" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="F60" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G60" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G59" s="8" t="s">
+      <c r="H60" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J60" s="7">
+        <v>1</v>
+      </c>
+      <c r="K60" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="J59" s="7">
-        <v>2</v>
-      </c>
-      <c r="K59" s="7"/>
-    </row>
-    <row r="60" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="11">
-        <f t="shared" ref="B60" si="2">ROW(B60) - ROW($B$2)</f>
-        <v>58</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="K60" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="11">
-        <f>ROW(B61) - ROW($B$2)</f>
-        <v>59</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J61" s="7">
-        <v>1</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
+++ b/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="286">
   <si>
     <t>#</t>
   </si>
@@ -171,6 +171,9 @@
     <t>J4, J5</t>
   </si>
   <si>
+    <t>J6</t>
+  </si>
+  <si>
     <t>J7</t>
   </si>
   <si>
@@ -336,6 +339,9 @@
     <t>Gold 250V 3A Straight Square Pins 2.5mm 2P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
+    <t>CABLE ADAPTER 6 POS</t>
+  </si>
+  <si>
     <t>Gold 250V 3A Straight Square Pins 2.5mm 3P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x3P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
@@ -594,6 +600,9 @@
     <t>X6511WV-02H-C60D30</t>
   </si>
   <si>
+    <t>TC2030-IDC</t>
+  </si>
+  <si>
     <t>X6511WV-03H-C60D30</t>
   </si>
   <si>
@@ -723,6 +732,9 @@
     <t>XKB</t>
   </si>
   <si>
+    <t>Tag-Connect</t>
+  </si>
+  <si>
     <t>YJYCOIN</t>
   </si>
   <si>
@@ -811,6 +823,12 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Tag Connect</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
   </si>
   <si>
     <t>Custom</t>
@@ -865,7 +883,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,6 +922,13 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1032,7 +1057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1069,11 +1094,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1362,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1386,9 +1420,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1402,25 +1436,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1436,19 +1470,19 @@
         <v>24</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
@@ -1458,7 +1492,7 @@
     <row r="4" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B55" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B56" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1468,19 +1502,19 @@
         <v>25</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -1500,19 +1534,19 @@
         <v>26</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -1532,19 +1566,19 @@
         <v>27</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -1564,19 +1598,19 @@
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -1596,19 +1630,19 @@
         <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J8" s="9">
         <v>11</v>
@@ -1628,19 +1662,19 @@
         <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -1660,19 +1694,19 @@
         <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
@@ -1692,19 +1726,19 @@
         <v>32</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J11" s="7">
         <v>11</v>
@@ -1724,19 +1758,19 @@
         <v>33</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -1756,19 +1790,19 @@
         <v>34</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J13" s="7">
         <v>4</v>
@@ -1788,19 +1822,19 @@
         <v>35</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>7</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -1820,19 +1854,19 @@
         <v>36</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
@@ -1852,19 +1886,19 @@
         <v>37</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>7</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1884,19 +1918,19 @@
         <v>38</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -1916,19 +1950,19 @@
         <v>39</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -1948,19 +1982,19 @@
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -1980,19 +2014,19 @@
         <v>41</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -2012,19 +2046,19 @@
         <v>42</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2044,19 +2078,19 @@
         <v>43</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -2076,19 +2110,19 @@
         <v>44</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J23" s="7">
         <v>4</v>
@@ -2108,19 +2142,19 @@
         <v>45</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -2140,19 +2174,19 @@
         <v>46</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -2172,19 +2206,19 @@
         <v>47</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J26" s="9">
         <v>1</v>
@@ -2204,19 +2238,19 @@
         <v>48</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -2236,1045 +2270,1079 @@
         <v>49</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="C29" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J29" s="9">
-        <v>1</v>
-      </c>
-      <c r="K29" s="9"/>
+      <c r="E29" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="15">
+        <v>1</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
-        <f>ROW(B30) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>231</v>
+      <c r="E30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>236</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J30" s="7">
-        <v>4</v>
-      </c>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>107</v>
+      <c r="E31" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H31" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>234</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="J31" s="9">
-        <v>1</v>
-      </c>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J31" s="7">
+        <v>4</v>
+      </c>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
-        <f>ROW(B32) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>108</v>
+      <c r="E32" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J32" s="7">
-        <v>1</v>
-      </c>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="J32" s="9">
+        <v>1</v>
+      </c>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B33) - ROW($B$2)</f>
         <v>31</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="9" t="s">
+      <c r="C33" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>235</v>
+      <c r="E33" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J33" s="9">
-        <v>7</v>
-      </c>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1</v>
+      </c>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
-        <f>ROW(B34) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="7" t="s">
+      <c r="C34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>236</v>
+      <c r="E34" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>239</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J34" s="7">
-        <v>5</v>
-      </c>
-      <c r="K34" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="J34" s="9">
+        <v>7</v>
+      </c>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$2)</f>
         <v>33</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="C35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>7</v>
+      <c r="E35" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J35" s="9">
-        <v>1</v>
-      </c>
-      <c r="K35" s="9"/>
+        <v>267</v>
+      </c>
+      <c r="J35" s="7">
+        <v>5</v>
+      </c>
+      <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
-        <f>ROW(B36) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="7" t="s">
+      <c r="C36" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>225</v>
+      <c r="E36" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J36" s="7">
-        <v>1</v>
-      </c>
-      <c r="K36" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="J36" s="9">
+        <v>1</v>
+      </c>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B37) - ROW($B$2)</f>
         <v>35</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="C37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="J37" s="9">
-        <v>1</v>
-      </c>
-      <c r="K37" s="9"/>
+      <c r="E37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J37" s="7">
+        <v>1</v>
+      </c>
+      <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
-        <f>ROW(B38) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="J38" s="7">
-        <v>1</v>
-      </c>
-      <c r="K38" s="7"/>
+      <c r="E38" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J38" s="9">
+        <v>1</v>
+      </c>
+      <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="J39" s="9">
-        <v>1</v>
-      </c>
-      <c r="K39" s="9"/>
+      <c r="E39" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="J39" s="7">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
-        <f>ROW(B40) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="7" t="s">
+      <c r="C40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="J40" s="7">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7"/>
+      <c r="E40" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J40" s="9">
+        <v>1</v>
+      </c>
+      <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
-      <c r="C41" s="13"/>
-      <c r="D41" s="9" t="s">
+      <c r="C41" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="J41" s="9">
-        <v>1</v>
-      </c>
-      <c r="K41" s="9"/>
+      <c r="E41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J41" s="7">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
-        <f>ROW(B42) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="7" t="s">
+      <c r="C42" s="13"/>
+      <c r="D42" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="J42" s="7">
-        <v>5</v>
-      </c>
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E42" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="J42" s="9">
+        <v>1</v>
+      </c>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="C43" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="J43" s="9">
-        <v>12</v>
-      </c>
-      <c r="K43" s="9"/>
-    </row>
-    <row r="44" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E43" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J43" s="7">
+        <v>5</v>
+      </c>
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
-        <f>ROW(B44) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="7" t="s">
+      <c r="C44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="J44" s="7">
-        <v>33</v>
-      </c>
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E44" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="9">
+        <v>12</v>
+      </c>
+      <c r="K44" s="9"/>
+    </row>
+    <row r="45" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$2)</f>
         <v>43</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="9" t="s">
+      <c r="C45" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="J45" s="9">
-        <v>5</v>
-      </c>
-      <c r="K45" s="9"/>
+      <c r="E45" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="J45" s="7">
+        <v>33</v>
+      </c>
+      <c r="K45" s="7"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
-        <f>ROW(B46) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="J46" s="7">
-        <v>2</v>
-      </c>
-      <c r="K46" s="7"/>
+      <c r="E46" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="J46" s="9">
+        <v>5</v>
+      </c>
+      <c r="K46" s="9"/>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="J47" s="9">
-        <v>8</v>
-      </c>
-      <c r="K47" s="9"/>
+      <c r="E47" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="J47" s="7">
+        <v>2</v>
+      </c>
+      <c r="K47" s="7"/>
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
-        <f>ROW(B48) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="C48" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G48" s="8" t="s">
+      <c r="E48" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="I48" s="8" t="s">
+      <c r="G48" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I48" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="J48" s="7">
-        <v>2</v>
-      </c>
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="9">
+        <v>8</v>
+      </c>
+      <c r="K48" s="9"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="10" t="s">
-        <v>125</v>
+      <c r="E49" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>238</v>
+        <v>270</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>241</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J49" s="9">
-        <v>1</v>
-      </c>
-      <c r="K49" s="9"/>
-    </row>
-    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J49" s="7">
+        <v>2</v>
+      </c>
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f>ROW(B50) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="C50" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>126</v>
+      <c r="E50" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>239</v>
+        <v>270</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J50" s="7">
-        <v>1</v>
-      </c>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J50" s="9">
+        <v>1</v>
+      </c>
+      <c r="K50" s="9"/>
+    </row>
+    <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>7</v>
+      <c r="E51" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J51" s="9">
-        <v>1</v>
-      </c>
-      <c r="K51" s="9"/>
+        <v>267</v>
+      </c>
+      <c r="J51" s="7">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7"/>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f>ROW(B52) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>227</v>
+      <c r="E52" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J52" s="7">
-        <v>1</v>
-      </c>
-      <c r="K52" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="J52" s="9">
+        <v>1</v>
+      </c>
+      <c r="K52" s="9"/>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>239</v>
+      <c r="E53" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J53" s="9">
-        <v>1</v>
-      </c>
-      <c r="K53" s="9"/>
+        <v>267</v>
+      </c>
+      <c r="J53" s="7">
+        <v>1</v>
+      </c>
+      <c r="K53" s="7"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f>ROW(B54) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>239</v>
+      <c r="E54" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J54" s="7">
-        <v>1</v>
-      </c>
-      <c r="K54" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="J54" s="9">
+        <v>1</v>
+      </c>
+      <c r="K54" s="9"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>227</v>
+      <c r="E55" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J55" s="9">
-        <v>1</v>
-      </c>
-      <c r="K55" s="9"/>
-    </row>
-    <row r="56" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="J55" s="7">
+        <v>1</v>
+      </c>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f>ROW(B56) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>239</v>
+      <c r="E56" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J56" s="7">
+        <v>267</v>
+      </c>
+      <c r="J56" s="9">
+        <v>1</v>
+      </c>
+      <c r="K56" s="9"/>
+    </row>
+    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="11">
+        <f>ROW(B57) - ROW($B$2)</f>
+        <v>55</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J57" s="7">
         <v>4</v>
       </c>
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="11">
-        <f t="shared" ref="B57" si="1">ROW(B57) - ROW($B$2)</f>
-        <v>55</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J57" s="9">
-        <v>1</v>
-      </c>
-      <c r="K57" s="9"/>
+      <c r="K57" s="7"/>
     </row>
     <row r="58" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
-        <f>ROW(B58) - ROW($B$2)</f>
+        <f t="shared" ref="B58" si="1">ROW(B58) - ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G58" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="H58" s="7" t="s">
-        <v>271</v>
+      <c r="G58" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>232</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J58" s="7">
+        <v>267</v>
+      </c>
+      <c r="J58" s="9">
+        <v>1</v>
+      </c>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="11">
+        <f>ROW(B59) - ROW($B$2)</f>
+        <v>57</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="J59" s="7">
         <v>2</v>
       </c>
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="11">
-        <f t="shared" ref="B59" si="2">ROW(B59) - ROW($B$2)</f>
-        <v>57</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="11">
+        <f t="shared" ref="B60" si="2">ROW(B60) - ROW($B$2)</f>
+        <v>58</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="11">
+        <f>ROW(B61) - ROW($B$2)</f>
+        <v>59</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="11">
-        <f>ROW(B60) - ROW($B$2)</f>
-        <v>58</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J60" s="7">
-        <v>1</v>
-      </c>
-      <c r="K60" s="14" t="s">
-        <v>276</v>
+      <c r="E61" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J61" s="7">
+        <v>1</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
+++ b/Design Files/Solenoid-Board-v2.0/BOM/Client-Solenoid-Board-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="284">
   <si>
     <t>#</t>
   </si>
@@ -859,6 +859,18 @@
   </si>
   <si>
     <t xml:space="preserve">Solenoid </t>
+  </si>
+  <si>
+    <t>R71, R72</t>
+  </si>
+  <si>
+    <t>RES 560 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-07560RL</t>
+  </si>
+  <si>
+    <t>560R</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1375,6 +1387,8 @@
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1458,7 +1472,7 @@
     <row r="4" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B55" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B56" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2868,412 +2882,443 @@
         <v>46</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>124</v>
+        <v>281</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>162</v>
+        <v>282</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="J48" s="7">
         <v>2</v>
       </c>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>125</v>
+      <c r="D49" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>238</v>
+      <c r="G49" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J49" s="9">
-        <v>1</v>
-      </c>
-      <c r="K49" s="9"/>
-    </row>
-    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="7">
+        <v>2</v>
+      </c>
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
-        <f>ROW(B50) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>126</v>
+      <c r="C50" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J50" s="7">
-        <v>1</v>
-      </c>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J50" s="9">
+        <v>1</v>
+      </c>
+      <c r="K50" s="9"/>
+    </row>
+    <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>7</v>
+      <c r="D51" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J51" s="9">
-        <v>1</v>
-      </c>
-      <c r="K51" s="9"/>
+      <c r="J51" s="7">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7"/>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
-        <f>ROW(B52) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>227</v>
+      <c r="D52" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J52" s="7">
-        <v>1</v>
-      </c>
-      <c r="K52" s="7"/>
+      <c r="J52" s="9">
+        <v>1</v>
+      </c>
+      <c r="K52" s="9"/>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>239</v>
+      <c r="D53" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>227</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J53" s="9">
-        <v>1</v>
-      </c>
-      <c r="K53" s="9"/>
+      <c r="J53" s="7">
+        <v>1</v>
+      </c>
+      <c r="K53" s="7"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
-        <f>ROW(B54) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="8" t="s">
+      <c r="D54" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G54" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="H54" s="7" t="s">
+      <c r="G54" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H54" s="9" t="s">
         <v>239</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J54" s="7">
-        <v>1</v>
-      </c>
-      <c r="K54" s="7"/>
+      <c r="J54" s="9">
+        <v>1</v>
+      </c>
+      <c r="K54" s="9"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>227</v>
+      <c r="D55" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J55" s="9">
-        <v>1</v>
-      </c>
-      <c r="K55" s="9"/>
-    </row>
-    <row r="56" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J55" s="7">
+        <v>1</v>
+      </c>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
-        <f>ROW(B56) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>239</v>
+      <c r="D56" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="J56" s="7">
-        <v>4</v>
-      </c>
-      <c r="K56" s="7"/>
+      <c r="J56" s="9">
+        <v>1</v>
+      </c>
+      <c r="K56" s="9"/>
     </row>
     <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
-        <f t="shared" ref="B57" si="1">ROW(B57) - ROW($B$2)</f>
+        <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="J57" s="9">
-        <v>1</v>
-      </c>
-      <c r="K57" s="9"/>
+      <c r="C57" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J57" s="7">
+        <v>4</v>
+      </c>
+      <c r="K57" s="7"/>
     </row>
     <row r="58" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
-        <f>ROW(B58) - ROW($B$2)</f>
+        <f t="shared" ref="B58" si="1">ROW(B58) - ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>269</v>
+      <c r="D58" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="G58" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>271</v>
+      <c r="G58" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>229</v>
       </c>
       <c r="I58" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="J58" s="7">
-        <v>2</v>
-      </c>
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="9">
+        <v>1</v>
+      </c>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
-        <f t="shared" ref="B59" si="2">ROW(B59) - ROW($B$2)</f>
+        <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>266</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>264</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J59" s="7">
+        <v>2</v>
+      </c>
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
-        <f>ROW(B60) - ROW($B$2)</f>
+        <f t="shared" ref="B60" si="2">ROW(B60) - ROW($B$2)</f>
         <v>58</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>266</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>264</v>
       </c>
       <c r="G60" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="11">
+        <f>ROW(B61) - ROW($B$2)</f>
+        <v>59</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G61" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="H60" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="J60" s="7">
-        <v>1</v>
-      </c>
-      <c r="K60" s="14" t="s">
+      <c r="H61" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J61" s="7">
+        <v>1</v>
+      </c>
+      <c r="K61" s="14" t="s">
         <v>276</v>
       </c>
     </row>
